--- a/public/plantilla-ficha-sst.xlsx
+++ b/public/plantilla-ficha-sst.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="41">
+  <numFmts count="0"/>
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -305,6 +306,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1033,7 +1038,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="366">
+  <cellXfs count="376">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1955,6 +1960,40 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2687,16 +2726,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="366" t="n"/>
+      <c r="D11" s="367" t="n"/>
+      <c r="E11" s="367" t="n"/>
+      <c r="F11" s="367" t="n"/>
+      <c r="G11" s="367" t="n"/>
+      <c r="H11" s="367" t="n"/>
+      <c r="I11" s="367" t="n"/>
+      <c r="J11" s="367" t="n"/>
+      <c r="K11" s="367" t="n"/>
+      <c r="L11" s="368" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2705,20 +2744,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="366" t="n"/>
+      <c r="D12" s="367" t="n"/>
+      <c r="E12" s="367" t="n"/>
+      <c r="F12" s="367" t="n"/>
+      <c r="G12" s="368" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="366" t="n"/>
+      <c r="K12" s="367" t="n"/>
+      <c r="L12" s="368" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2727,20 +2766,20 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="89" t="n"/>
+      <c r="C13" s="366" t="n"/>
+      <c r="D13" s="367" t="n"/>
+      <c r="E13" s="367" t="n"/>
+      <c r="F13" s="367" t="n"/>
+      <c r="G13" s="368" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>N° de contrato</t>
         </is>
       </c>
       <c r="I13" s="89" t="n"/>
-      <c r="J13" s="68" t="n"/>
-      <c r="K13" s="93" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="J13" s="366" t="n"/>
+      <c r="K13" s="367" t="n"/>
+      <c r="L13" s="368" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2749,20 +2788,20 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="93" t="n"/>
-      <c r="E14" s="93" t="n"/>
-      <c r="F14" s="93" t="n"/>
-      <c r="G14" s="89" t="n"/>
+      <c r="C14" s="366" t="n"/>
+      <c r="D14" s="367" t="n"/>
+      <c r="E14" s="367" t="n"/>
+      <c r="F14" s="367" t="n"/>
+      <c r="G14" s="368" t="n"/>
       <c r="H14" s="59" t="inlineStr">
         <is>
           <t>Tipo de obra</t>
         </is>
       </c>
       <c r="I14" s="89" t="n"/>
-      <c r="J14" s="68" t="n"/>
-      <c r="K14" s="93" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="J14" s="366" t="n"/>
+      <c r="K14" s="367" t="n"/>
+      <c r="L14" s="368" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="127">
       <c r="A15" s="59" t="inlineStr">
@@ -2771,24 +2810,24 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="69" t="n"/>
-      <c r="D15" s="89" t="n"/>
+      <c r="C15" s="369" t="n"/>
+      <c r="D15" s="368" t="n"/>
       <c r="E15" s="59" t="inlineStr">
         <is>
           <t>Terminación prevista</t>
         </is>
       </c>
       <c r="F15" s="89" t="n"/>
-      <c r="G15" s="69" t="n"/>
-      <c r="H15" s="89" t="n"/>
+      <c r="G15" s="369" t="n"/>
+      <c r="H15" s="368" t="n"/>
       <c r="I15" s="59" t="inlineStr">
         <is>
           <t>Trabajadores previstos</t>
         </is>
       </c>
       <c r="J15" s="89" t="n"/>
-      <c r="K15" s="69" t="n"/>
-      <c r="L15" s="89" t="n"/>
+      <c r="K15" s="369" t="n"/>
+      <c r="L15" s="368" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="127">
       <c r="A16" s="59" t="inlineStr">
@@ -2797,24 +2836,24 @@
         </is>
       </c>
       <c r="B16" s="89" t="n"/>
-      <c r="C16" s="69" t="n"/>
-      <c r="D16" s="89" t="n"/>
+      <c r="C16" s="369" t="n"/>
+      <c r="D16" s="368" t="n"/>
       <c r="E16" s="59" t="inlineStr">
         <is>
           <t>Días por semana</t>
         </is>
       </c>
       <c r="F16" s="89" t="n"/>
-      <c r="G16" s="69" t="n"/>
-      <c r="H16" s="89" t="n"/>
+      <c r="G16" s="369" t="n"/>
+      <c r="H16" s="368" t="n"/>
       <c r="I16" s="59" t="inlineStr">
         <is>
           <t>Turnos</t>
         </is>
       </c>
       <c r="J16" s="89" t="n"/>
-      <c r="K16" s="69" t="n"/>
-      <c r="L16" s="89" t="n"/>
+      <c r="K16" s="369" t="n"/>
+      <c r="L16" s="368" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="127">
       <c r="A17" s="137" t="inlineStr">
@@ -2841,20 +2880,20 @@
         </is>
       </c>
       <c r="B18" s="89" t="n"/>
-      <c r="C18" s="68" t="n"/>
-      <c r="D18" s="93" t="n"/>
-      <c r="E18" s="93" t="n"/>
-      <c r="F18" s="93" t="n"/>
-      <c r="G18" s="89" t="n"/>
+      <c r="C18" s="366" t="n"/>
+      <c r="D18" s="367" t="n"/>
+      <c r="E18" s="367" t="n"/>
+      <c r="F18" s="367" t="n"/>
+      <c r="G18" s="368" t="n"/>
       <c r="H18" s="59" t="inlineStr">
         <is>
           <t>Clase de riesgo</t>
         </is>
       </c>
       <c r="I18" s="89" t="n"/>
-      <c r="J18" s="69" t="n"/>
-      <c r="K18" s="93" t="n"/>
-      <c r="L18" s="89" t="n"/>
+      <c r="J18" s="369" t="n"/>
+      <c r="K18" s="367" t="n"/>
+      <c r="L18" s="368" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1" s="127">
       <c r="A19" s="59" t="inlineStr">
@@ -2863,20 +2902,20 @@
         </is>
       </c>
       <c r="B19" s="89" t="n"/>
-      <c r="C19" s="68" t="n"/>
-      <c r="D19" s="93" t="n"/>
-      <c r="E19" s="93" t="n"/>
-      <c r="F19" s="93" t="n"/>
-      <c r="G19" s="89" t="n"/>
+      <c r="C19" s="366" t="n"/>
+      <c r="D19" s="367" t="n"/>
+      <c r="E19" s="367" t="n"/>
+      <c r="F19" s="367" t="n"/>
+      <c r="G19" s="368" t="n"/>
       <c r="H19" s="59" t="inlineStr">
         <is>
           <t>Fecha de afiliación</t>
         </is>
       </c>
       <c r="I19" s="89" t="n"/>
-      <c r="J19" s="69" t="n"/>
-      <c r="K19" s="93" t="n"/>
-      <c r="L19" s="89" t="n"/>
+      <c r="J19" s="369" t="n"/>
+      <c r="K19" s="367" t="n"/>
+      <c r="L19" s="368" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="127">
       <c r="A20" s="59" t="inlineStr">
@@ -2885,20 +2924,20 @@
         </is>
       </c>
       <c r="B20" s="89" t="n"/>
-      <c r="C20" s="68" t="n"/>
-      <c r="D20" s="93" t="n"/>
-      <c r="E20" s="93" t="n"/>
-      <c r="F20" s="93" t="n"/>
-      <c r="G20" s="89" t="n"/>
+      <c r="C20" s="366" t="n"/>
+      <c r="D20" s="367" t="n"/>
+      <c r="E20" s="367" t="n"/>
+      <c r="F20" s="367" t="n"/>
+      <c r="G20" s="368" t="n"/>
       <c r="H20" s="59" t="inlineStr">
         <is>
           <t>Documento</t>
         </is>
       </c>
       <c r="I20" s="89" t="n"/>
-      <c r="J20" s="68" t="n"/>
-      <c r="K20" s="93" t="n"/>
-      <c r="L20" s="89" t="n"/>
+      <c r="J20" s="366" t="n"/>
+      <c r="K20" s="367" t="n"/>
+      <c r="L20" s="368" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1" s="127">
       <c r="A21" s="59" t="inlineStr">
@@ -2907,20 +2946,20 @@
         </is>
       </c>
       <c r="B21" s="89" t="n"/>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="93" t="n"/>
-      <c r="E21" s="93" t="n"/>
-      <c r="F21" s="93" t="n"/>
-      <c r="G21" s="89" t="n"/>
+      <c r="C21" s="366" t="n"/>
+      <c r="D21" s="367" t="n"/>
+      <c r="E21" s="367" t="n"/>
+      <c r="F21" s="367" t="n"/>
+      <c r="G21" s="368" t="n"/>
       <c r="H21" s="59" t="inlineStr">
         <is>
           <t>Licencia en SST N°</t>
         </is>
       </c>
       <c r="I21" s="89" t="n"/>
-      <c r="J21" s="68" t="n"/>
-      <c r="K21" s="93" t="n"/>
-      <c r="L21" s="89" t="n"/>
+      <c r="J21" s="366" t="n"/>
+      <c r="K21" s="367" t="n"/>
+      <c r="L21" s="368" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1" s="127">
       <c r="A22" s="59" t="inlineStr">
@@ -2929,20 +2968,20 @@
         </is>
       </c>
       <c r="B22" s="89" t="n"/>
-      <c r="C22" s="69" t="n"/>
-      <c r="D22" s="93" t="n"/>
-      <c r="E22" s="93" t="n"/>
-      <c r="F22" s="93" t="n"/>
-      <c r="G22" s="89" t="n"/>
+      <c r="C22" s="369" t="n"/>
+      <c r="D22" s="367" t="n"/>
+      <c r="E22" s="367" t="n"/>
+      <c r="F22" s="367" t="n"/>
+      <c r="G22" s="368" t="n"/>
       <c r="H22" s="59" t="inlineStr">
         <is>
           <t>Teléfono del responsable</t>
         </is>
       </c>
       <c r="I22" s="89" t="n"/>
-      <c r="J22" s="68" t="n"/>
-      <c r="K22" s="93" t="n"/>
-      <c r="L22" s="89" t="n"/>
+      <c r="J22" s="366" t="n"/>
+      <c r="K22" s="367" t="n"/>
+      <c r="L22" s="368" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="127">
       <c r="A23" s="59" t="inlineStr">
@@ -2951,20 +2990,20 @@
         </is>
       </c>
       <c r="B23" s="89" t="n"/>
-      <c r="C23" s="68" t="n"/>
-      <c r="D23" s="93" t="n"/>
-      <c r="E23" s="93" t="n"/>
-      <c r="F23" s="93" t="n"/>
-      <c r="G23" s="89" t="n"/>
+      <c r="C23" s="366" t="n"/>
+      <c r="D23" s="367" t="n"/>
+      <c r="E23" s="367" t="n"/>
+      <c r="F23" s="367" t="n"/>
+      <c r="G23" s="368" t="n"/>
       <c r="H23" s="59" t="inlineStr">
         <is>
           <t>Teléfono del residente</t>
         </is>
       </c>
       <c r="I23" s="89" t="n"/>
-      <c r="J23" s="68" t="n"/>
-      <c r="K23" s="93" t="n"/>
-      <c r="L23" s="89" t="n"/>
+      <c r="J23" s="366" t="n"/>
+      <c r="K23" s="367" t="n"/>
+      <c r="L23" s="368" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="127">
       <c r="A24" s="59" t="inlineStr">
@@ -2973,20 +3012,20 @@
         </is>
       </c>
       <c r="B24" s="89" t="n"/>
-      <c r="C24" s="69" t="n"/>
-      <c r="D24" s="93" t="n"/>
-      <c r="E24" s="93" t="n"/>
-      <c r="F24" s="93" t="n"/>
-      <c r="G24" s="89" t="n"/>
+      <c r="C24" s="369" t="n"/>
+      <c r="D24" s="367" t="n"/>
+      <c r="E24" s="367" t="n"/>
+      <c r="F24" s="367" t="n"/>
+      <c r="G24" s="368" t="n"/>
       <c r="H24" s="59" t="inlineStr">
         <is>
           <t>Vigente hasta</t>
         </is>
       </c>
       <c r="I24" s="89" t="n"/>
-      <c r="J24" s="69" t="n"/>
-      <c r="K24" s="93" t="n"/>
-      <c r="L24" s="89" t="n"/>
+      <c r="J24" s="369" t="n"/>
+      <c r="K24" s="367" t="n"/>
+      <c r="L24" s="368" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="127">
       <c r="A25" s="59" t="inlineStr">
@@ -2995,20 +3034,20 @@
         </is>
       </c>
       <c r="B25" s="89" t="n"/>
-      <c r="C25" s="69" t="n"/>
-      <c r="D25" s="93" t="n"/>
-      <c r="E25" s="93" t="n"/>
-      <c r="F25" s="93" t="n"/>
-      <c r="G25" s="89" t="n"/>
+      <c r="C25" s="369" t="n"/>
+      <c r="D25" s="367" t="n"/>
+      <c r="E25" s="367" t="n"/>
+      <c r="F25" s="367" t="n"/>
+      <c r="G25" s="368" t="n"/>
       <c r="H25" s="59" t="inlineStr">
         <is>
           <t>Brigada de emergencias</t>
         </is>
       </c>
       <c r="I25" s="89" t="n"/>
-      <c r="J25" s="69" t="n"/>
-      <c r="K25" s="93" t="n"/>
-      <c r="L25" s="89" t="n"/>
+      <c r="J25" s="369" t="n"/>
+      <c r="K25" s="367" t="n"/>
+      <c r="L25" s="368" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="127">
       <c r="A26" s="137" t="inlineStr">
@@ -3029,28 +3068,28 @@
       <c r="L26" s="97" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="127">
-      <c r="A27" s="230" t="inlineStr">
+      <c r="A27" s="370" t="inlineStr">
         <is>
           <t>☐ Trabajo en alturas</t>
         </is>
       </c>
       <c r="B27" s="98" t="n"/>
       <c r="C27" s="97" t="n"/>
-      <c r="D27" s="230" t="inlineStr">
+      <c r="D27" s="370" t="inlineStr">
         <is>
           <t>☐ Excavaciones y zanjas</t>
         </is>
       </c>
       <c r="E27" s="98" t="n"/>
       <c r="F27" s="97" t="n"/>
-      <c r="G27" s="230" t="inlineStr">
+      <c r="G27" s="370" t="inlineStr">
         <is>
           <t>☐ Trabajos eléctricos</t>
         </is>
       </c>
       <c r="H27" s="98" t="n"/>
       <c r="I27" s="97" t="n"/>
-      <c r="J27" s="230" t="inlineStr">
+      <c r="J27" s="370" t="inlineStr">
         <is>
           <t>☐ Trabajo en caliente (soldadura, corte)</t>
         </is>
@@ -3059,28 +3098,28 @@
       <c r="L27" s="97" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="127">
-      <c r="A28" s="230" t="inlineStr">
+      <c r="A28" s="370" t="inlineStr">
         <is>
           <t>☐ Espacios confinados</t>
         </is>
       </c>
       <c r="B28" s="98" t="n"/>
       <c r="C28" s="97" t="n"/>
-      <c r="D28" s="230" t="inlineStr">
+      <c r="D28" s="370" t="inlineStr">
         <is>
           <t>☐ Izaje de cargas</t>
         </is>
       </c>
       <c r="E28" s="98" t="n"/>
       <c r="F28" s="97" t="n"/>
-      <c r="G28" s="230" t="inlineStr">
+      <c r="G28" s="370" t="inlineStr">
         <is>
           <t>☐ Maquinaria pesada y vehículos</t>
         </is>
       </c>
       <c r="H28" s="98" t="n"/>
       <c r="I28" s="97" t="n"/>
-      <c r="J28" s="230" t="inlineStr">
+      <c r="J28" s="370" t="inlineStr">
         <is>
           <t>☐ Manejo de sustancias químicas</t>
         </is>
@@ -3089,28 +3128,28 @@
       <c r="L28" s="97" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="127">
-      <c r="A29" s="230" t="inlineStr">
+      <c r="A29" s="370" t="inlineStr">
         <is>
           <t>☐ Demoliciones</t>
         </is>
       </c>
       <c r="B29" s="98" t="n"/>
       <c r="C29" s="97" t="n"/>
-      <c r="D29" s="230" t="inlineStr">
+      <c r="D29" s="370" t="inlineStr">
         <is>
           <t>☐ Andamios y estructuras temporales</t>
         </is>
       </c>
       <c r="E29" s="98" t="n"/>
       <c r="F29" s="97" t="n"/>
-      <c r="G29" s="230" t="inlineStr">
+      <c r="G29" s="370" t="inlineStr">
         <is>
           <t>☐ Tránsito vehicular y peatonal</t>
         </is>
       </c>
       <c r="H29" s="98" t="n"/>
       <c r="I29" s="97" t="n"/>
-      <c r="J29" s="230" t="inlineStr">
+      <c r="J29" s="370" t="inlineStr">
         <is>
           <t>☐ Otro: ____________</t>
         </is>
@@ -3171,10 +3210,10 @@
       <c r="L31" s="348" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1" s="127">
-      <c r="A32" s="306" t="n">
+      <c r="A32" s="371" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="230" t="inlineStr">
+      <c r="B32" s="370" t="inlineStr">
         <is>
           <t>Política de SST firmada y divulgada</t>
         </is>
@@ -3183,18 +3222,18 @@
       <c r="D32" s="98" t="n"/>
       <c r="E32" s="98" t="n"/>
       <c r="F32" s="97" t="n"/>
-      <c r="G32" s="306" t="n"/>
-      <c r="H32" s="97" t="n"/>
-      <c r="I32" s="306" t="n"/>
-      <c r="J32" s="97" t="n"/>
-      <c r="K32" s="230" t="n"/>
-      <c r="L32" s="97" t="n"/>
+      <c r="G32" s="372" t="n"/>
+      <c r="H32" s="373" t="n"/>
+      <c r="I32" s="372" t="n"/>
+      <c r="J32" s="373" t="n"/>
+      <c r="K32" s="374" t="n"/>
+      <c r="L32" s="373" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1" s="127">
-      <c r="A33" s="306" t="n">
+      <c r="A33" s="371" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="230" t="inlineStr">
+      <c r="B33" s="370" t="inlineStr">
         <is>
           <t>Matriz de peligros y valoración de riesgos</t>
         </is>
@@ -3203,18 +3242,18 @@
       <c r="D33" s="98" t="n"/>
       <c r="E33" s="98" t="n"/>
       <c r="F33" s="97" t="n"/>
-      <c r="G33" s="306" t="n"/>
-      <c r="H33" s="97" t="n"/>
-      <c r="I33" s="306" t="n"/>
-      <c r="J33" s="97" t="n"/>
-      <c r="K33" s="230" t="n"/>
-      <c r="L33" s="97" t="n"/>
+      <c r="G33" s="372" t="n"/>
+      <c r="H33" s="373" t="n"/>
+      <c r="I33" s="372" t="n"/>
+      <c r="J33" s="373" t="n"/>
+      <c r="K33" s="374" t="n"/>
+      <c r="L33" s="373" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1" s="127">
-      <c r="A34" s="306" t="n">
+      <c r="A34" s="371" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="230" t="inlineStr">
+      <c r="B34" s="370" t="inlineStr">
         <is>
           <t>Plan anual de trabajo del SG-SST</t>
         </is>
@@ -3223,18 +3262,18 @@
       <c r="D34" s="98" t="n"/>
       <c r="E34" s="98" t="n"/>
       <c r="F34" s="97" t="n"/>
-      <c r="G34" s="306" t="n"/>
-      <c r="H34" s="97" t="n"/>
-      <c r="I34" s="306" t="n"/>
-      <c r="J34" s="97" t="n"/>
-      <c r="K34" s="230" t="n"/>
-      <c r="L34" s="97" t="n"/>
+      <c r="G34" s="372" t="n"/>
+      <c r="H34" s="373" t="n"/>
+      <c r="I34" s="372" t="n"/>
+      <c r="J34" s="373" t="n"/>
+      <c r="K34" s="374" t="n"/>
+      <c r="L34" s="373" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1" s="127">
-      <c r="A35" s="306" t="n">
+      <c r="A35" s="371" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="230" t="inlineStr">
+      <c r="B35" s="370" t="inlineStr">
         <is>
           <t>Reglamento de higiene y seguridad industrial</t>
         </is>
@@ -3243,18 +3282,18 @@
       <c r="D35" s="98" t="n"/>
       <c r="E35" s="98" t="n"/>
       <c r="F35" s="97" t="n"/>
-      <c r="G35" s="306" t="n"/>
-      <c r="H35" s="97" t="n"/>
-      <c r="I35" s="306" t="n"/>
-      <c r="J35" s="97" t="n"/>
-      <c r="K35" s="230" t="n"/>
-      <c r="L35" s="97" t="n"/>
+      <c r="G35" s="372" t="n"/>
+      <c r="H35" s="373" t="n"/>
+      <c r="I35" s="372" t="n"/>
+      <c r="J35" s="373" t="n"/>
+      <c r="K35" s="374" t="n"/>
+      <c r="L35" s="373" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1" s="127">
-      <c r="A36" s="306" t="n">
+      <c r="A36" s="371" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="230" t="inlineStr">
+      <c r="B36" s="370" t="inlineStr">
         <is>
           <t>Plan de emergencias</t>
         </is>
@@ -3263,18 +3302,18 @@
       <c r="D36" s="98" t="n"/>
       <c r="E36" s="98" t="n"/>
       <c r="F36" s="97" t="n"/>
-      <c r="G36" s="306" t="n"/>
-      <c r="H36" s="97" t="n"/>
-      <c r="I36" s="306" t="n"/>
-      <c r="J36" s="97" t="n"/>
-      <c r="K36" s="230" t="n"/>
-      <c r="L36" s="97" t="n"/>
+      <c r="G36" s="372" t="n"/>
+      <c r="H36" s="373" t="n"/>
+      <c r="I36" s="372" t="n"/>
+      <c r="J36" s="373" t="n"/>
+      <c r="K36" s="374" t="n"/>
+      <c r="L36" s="373" t="n"/>
     </row>
     <row r="37" ht="19" customHeight="1" s="127">
-      <c r="A37" s="306" t="n">
+      <c r="A37" s="371" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="230" t="inlineStr">
+      <c r="B37" s="370" t="inlineStr">
         <is>
           <t>Programa de capacitación y entrenamiento</t>
         </is>
@@ -3283,18 +3322,18 @@
       <c r="D37" s="98" t="n"/>
       <c r="E37" s="98" t="n"/>
       <c r="F37" s="97" t="n"/>
-      <c r="G37" s="306" t="n"/>
-      <c r="H37" s="97" t="n"/>
-      <c r="I37" s="306" t="n"/>
-      <c r="J37" s="97" t="n"/>
-      <c r="K37" s="230" t="n"/>
-      <c r="L37" s="97" t="n"/>
+      <c r="G37" s="372" t="n"/>
+      <c r="H37" s="373" t="n"/>
+      <c r="I37" s="372" t="n"/>
+      <c r="J37" s="373" t="n"/>
+      <c r="K37" s="374" t="n"/>
+      <c r="L37" s="373" t="n"/>
     </row>
     <row r="38" ht="19" customHeight="1" s="127">
-      <c r="A38" s="306" t="n">
+      <c r="A38" s="371" t="n">
         <v>7</v>
       </c>
-      <c r="B38" s="230" t="inlineStr">
+      <c r="B38" s="370" t="inlineStr">
         <is>
           <t>Procedimiento de permisos de trabajo de alto riesgo</t>
         </is>
@@ -3303,18 +3342,18 @@
       <c r="D38" s="98" t="n"/>
       <c r="E38" s="98" t="n"/>
       <c r="F38" s="97" t="n"/>
-      <c r="G38" s="306" t="n"/>
-      <c r="H38" s="97" t="n"/>
-      <c r="I38" s="306" t="n"/>
-      <c r="J38" s="97" t="n"/>
-      <c r="K38" s="230" t="n"/>
-      <c r="L38" s="97" t="n"/>
+      <c r="G38" s="372" t="n"/>
+      <c r="H38" s="373" t="n"/>
+      <c r="I38" s="372" t="n"/>
+      <c r="J38" s="373" t="n"/>
+      <c r="K38" s="374" t="n"/>
+      <c r="L38" s="373" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1" s="127">
-      <c r="A39" s="306" t="n">
+      <c r="A39" s="371" t="n">
         <v>8</v>
       </c>
-      <c r="B39" s="230" t="inlineStr">
+      <c r="B39" s="370" t="inlineStr">
         <is>
           <t>Programa de trabajo en alturas</t>
         </is>
@@ -3323,18 +3362,18 @@
       <c r="D39" s="98" t="n"/>
       <c r="E39" s="98" t="n"/>
       <c r="F39" s="97" t="n"/>
-      <c r="G39" s="306" t="n"/>
-      <c r="H39" s="97" t="n"/>
-      <c r="I39" s="306" t="n"/>
-      <c r="J39" s="97" t="n"/>
-      <c r="K39" s="230" t="n"/>
-      <c r="L39" s="97" t="n"/>
+      <c r="G39" s="372" t="n"/>
+      <c r="H39" s="373" t="n"/>
+      <c r="I39" s="372" t="n"/>
+      <c r="J39" s="373" t="n"/>
+      <c r="K39" s="374" t="n"/>
+      <c r="L39" s="373" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1" s="127">
-      <c r="A40" s="306" t="n">
+      <c r="A40" s="371" t="n">
         <v>9</v>
       </c>
-      <c r="B40" s="230" t="inlineStr">
+      <c r="B40" s="370" t="inlineStr">
         <is>
           <t>Plan Estratégico de Seguridad Vial (si aplica)</t>
         </is>
@@ -3343,18 +3382,18 @@
       <c r="D40" s="98" t="n"/>
       <c r="E40" s="98" t="n"/>
       <c r="F40" s="97" t="n"/>
-      <c r="G40" s="306" t="n"/>
-      <c r="H40" s="97" t="n"/>
-      <c r="I40" s="306" t="n"/>
-      <c r="J40" s="97" t="n"/>
-      <c r="K40" s="230" t="n"/>
-      <c r="L40" s="97" t="n"/>
+      <c r="G40" s="372" t="n"/>
+      <c r="H40" s="373" t="n"/>
+      <c r="I40" s="372" t="n"/>
+      <c r="J40" s="373" t="n"/>
+      <c r="K40" s="374" t="n"/>
+      <c r="L40" s="373" t="n"/>
     </row>
     <row r="41" ht="19" customHeight="1" s="127">
-      <c r="A41" s="306" t="n">
+      <c r="A41" s="371" t="n">
         <v>10</v>
       </c>
-      <c r="B41" s="230" t="inlineStr">
+      <c r="B41" s="370" t="inlineStr">
         <is>
           <t>Exámenes médicos ocupacionales de ingreso</t>
         </is>
@@ -3363,12 +3402,12 @@
       <c r="D41" s="98" t="n"/>
       <c r="E41" s="98" t="n"/>
       <c r="F41" s="97" t="n"/>
-      <c r="G41" s="306" t="n"/>
-      <c r="H41" s="97" t="n"/>
-      <c r="I41" s="306" t="n"/>
-      <c r="J41" s="97" t="n"/>
-      <c r="K41" s="230" t="n"/>
-      <c r="L41" s="97" t="n"/>
+      <c r="G41" s="372" t="n"/>
+      <c r="H41" s="373" t="n"/>
+      <c r="I41" s="372" t="n"/>
+      <c r="J41" s="373" t="n"/>
+      <c r="K41" s="374" t="n"/>
+      <c r="L41" s="373" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="127">
       <c r="A42" s="137" t="inlineStr">
@@ -3419,10 +3458,10 @@
       <c r="L43" s="348" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1" s="127">
-      <c r="A44" s="306" t="n">
+      <c r="A44" s="371" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="230" t="inlineStr">
+      <c r="B44" s="370" t="inlineStr">
         <is>
           <t>Bomberos</t>
         </is>
@@ -3430,19 +3469,19 @@
       <c r="C44" s="98" t="n"/>
       <c r="D44" s="98" t="n"/>
       <c r="E44" s="97" t="n"/>
-      <c r="F44" s="306" t="n"/>
-      <c r="G44" s="97" t="n"/>
-      <c r="H44" s="230" t="n"/>
-      <c r="I44" s="98" t="n"/>
-      <c r="J44" s="98" t="n"/>
-      <c r="K44" s="98" t="n"/>
-      <c r="L44" s="97" t="n"/>
+      <c r="F44" s="372" t="n"/>
+      <c r="G44" s="373" t="n"/>
+      <c r="H44" s="374" t="n"/>
+      <c r="I44" s="375" t="n"/>
+      <c r="J44" s="375" t="n"/>
+      <c r="K44" s="375" t="n"/>
+      <c r="L44" s="373" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1" s="127">
-      <c r="A45" s="306" t="n">
+      <c r="A45" s="371" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="230" t="inlineStr">
+      <c r="B45" s="370" t="inlineStr">
         <is>
           <t>Policía</t>
         </is>
@@ -3450,19 +3489,19 @@
       <c r="C45" s="98" t="n"/>
       <c r="D45" s="98" t="n"/>
       <c r="E45" s="97" t="n"/>
-      <c r="F45" s="306" t="n"/>
-      <c r="G45" s="97" t="n"/>
-      <c r="H45" s="230" t="n"/>
-      <c r="I45" s="98" t="n"/>
-      <c r="J45" s="98" t="n"/>
-      <c r="K45" s="98" t="n"/>
-      <c r="L45" s="97" t="n"/>
+      <c r="F45" s="372" t="n"/>
+      <c r="G45" s="373" t="n"/>
+      <c r="H45" s="374" t="n"/>
+      <c r="I45" s="375" t="n"/>
+      <c r="J45" s="375" t="n"/>
+      <c r="K45" s="375" t="n"/>
+      <c r="L45" s="373" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1" s="127">
-      <c r="A46" s="306" t="n">
+      <c r="A46" s="371" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="230" t="inlineStr">
+      <c r="B46" s="370" t="inlineStr">
         <is>
           <t>Cruz Roja o Defensa Civil</t>
         </is>
@@ -3470,19 +3509,19 @@
       <c r="C46" s="98" t="n"/>
       <c r="D46" s="98" t="n"/>
       <c r="E46" s="97" t="n"/>
-      <c r="F46" s="306" t="n"/>
-      <c r="G46" s="97" t="n"/>
-      <c r="H46" s="230" t="n"/>
-      <c r="I46" s="98" t="n"/>
-      <c r="J46" s="98" t="n"/>
-      <c r="K46" s="98" t="n"/>
-      <c r="L46" s="97" t="n"/>
+      <c r="F46" s="372" t="n"/>
+      <c r="G46" s="373" t="n"/>
+      <c r="H46" s="374" t="n"/>
+      <c r="I46" s="375" t="n"/>
+      <c r="J46" s="375" t="n"/>
+      <c r="K46" s="375" t="n"/>
+      <c r="L46" s="373" t="n"/>
     </row>
     <row r="47" ht="19" customHeight="1" s="127">
-      <c r="A47" s="306" t="n">
+      <c r="A47" s="371" t="n">
         <v>4</v>
       </c>
-      <c r="B47" s="230" t="inlineStr">
+      <c r="B47" s="370" t="inlineStr">
         <is>
           <t>Hospital o clínica más cercana</t>
         </is>
@@ -3490,19 +3529,19 @@
       <c r="C47" s="98" t="n"/>
       <c r="D47" s="98" t="n"/>
       <c r="E47" s="97" t="n"/>
-      <c r="F47" s="306" t="n"/>
-      <c r="G47" s="97" t="n"/>
-      <c r="H47" s="230" t="n"/>
-      <c r="I47" s="98" t="n"/>
-      <c r="J47" s="98" t="n"/>
-      <c r="K47" s="98" t="n"/>
-      <c r="L47" s="97" t="n"/>
+      <c r="F47" s="372" t="n"/>
+      <c r="G47" s="373" t="n"/>
+      <c r="H47" s="374" t="n"/>
+      <c r="I47" s="375" t="n"/>
+      <c r="J47" s="375" t="n"/>
+      <c r="K47" s="375" t="n"/>
+      <c r="L47" s="373" t="n"/>
     </row>
     <row r="48" ht="19" customHeight="1" s="127">
-      <c r="A48" s="306" t="n">
+      <c r="A48" s="371" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="230" t="inlineStr">
+      <c r="B48" s="370" t="inlineStr">
         <is>
           <t>Línea de la ARL</t>
         </is>
@@ -3510,19 +3549,19 @@
       <c r="C48" s="98" t="n"/>
       <c r="D48" s="98" t="n"/>
       <c r="E48" s="97" t="n"/>
-      <c r="F48" s="306" t="n"/>
-      <c r="G48" s="97" t="n"/>
-      <c r="H48" s="230" t="n"/>
-      <c r="I48" s="98" t="n"/>
-      <c r="J48" s="98" t="n"/>
-      <c r="K48" s="98" t="n"/>
-      <c r="L48" s="97" t="n"/>
+      <c r="F48" s="372" t="n"/>
+      <c r="G48" s="373" t="n"/>
+      <c r="H48" s="374" t="n"/>
+      <c r="I48" s="375" t="n"/>
+      <c r="J48" s="375" t="n"/>
+      <c r="K48" s="375" t="n"/>
+      <c r="L48" s="373" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1" s="127">
-      <c r="A49" s="306" t="n">
+      <c r="A49" s="371" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="230" t="inlineStr">
+      <c r="B49" s="370" t="inlineStr">
         <is>
           <t>Ambulancia</t>
         </is>
@@ -3530,19 +3569,19 @@
       <c r="C49" s="98" t="n"/>
       <c r="D49" s="98" t="n"/>
       <c r="E49" s="97" t="n"/>
-      <c r="F49" s="306" t="n"/>
-      <c r="G49" s="97" t="n"/>
-      <c r="H49" s="230" t="n"/>
-      <c r="I49" s="98" t="n"/>
-      <c r="J49" s="98" t="n"/>
-      <c r="K49" s="98" t="n"/>
-      <c r="L49" s="97" t="n"/>
+      <c r="F49" s="372" t="n"/>
+      <c r="G49" s="373" t="n"/>
+      <c r="H49" s="374" t="n"/>
+      <c r="I49" s="375" t="n"/>
+      <c r="J49" s="375" t="n"/>
+      <c r="K49" s="375" t="n"/>
+      <c r="L49" s="373" t="n"/>
     </row>
     <row r="50" ht="19" customHeight="1" s="127">
-      <c r="A50" s="306" t="n">
+      <c r="A50" s="371" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="230" t="inlineStr">
+      <c r="B50" s="370" t="inlineStr">
         <is>
           <t>Dirección Territorial del Ministerio de Trabajo</t>
         </is>
@@ -3550,19 +3589,19 @@
       <c r="C50" s="98" t="n"/>
       <c r="D50" s="98" t="n"/>
       <c r="E50" s="97" t="n"/>
-      <c r="F50" s="306" t="n"/>
-      <c r="G50" s="97" t="n"/>
-      <c r="H50" s="230" t="n"/>
-      <c r="I50" s="98" t="n"/>
-      <c r="J50" s="98" t="n"/>
-      <c r="K50" s="98" t="n"/>
-      <c r="L50" s="97" t="n"/>
+      <c r="F50" s="372" t="n"/>
+      <c r="G50" s="373" t="n"/>
+      <c r="H50" s="374" t="n"/>
+      <c r="I50" s="375" t="n"/>
+      <c r="J50" s="375" t="n"/>
+      <c r="K50" s="375" t="n"/>
+      <c r="L50" s="373" t="n"/>
     </row>
     <row r="51" ht="19" customHeight="1" s="127">
-      <c r="A51" s="306" t="n">
+      <c r="A51" s="371" t="n">
         <v>8</v>
       </c>
-      <c r="B51" s="230" t="inlineStr">
+      <c r="B51" s="370" t="inlineStr">
         <is>
           <t>Otro</t>
         </is>
@@ -3570,13 +3609,13 @@
       <c r="C51" s="98" t="n"/>
       <c r="D51" s="98" t="n"/>
       <c r="E51" s="97" t="n"/>
-      <c r="F51" s="306" t="n"/>
-      <c r="G51" s="97" t="n"/>
-      <c r="H51" s="230" t="n"/>
-      <c r="I51" s="98" t="n"/>
-      <c r="J51" s="98" t="n"/>
-      <c r="K51" s="98" t="n"/>
-      <c r="L51" s="97" t="n"/>
+      <c r="F51" s="372" t="n"/>
+      <c r="G51" s="373" t="n"/>
+      <c r="H51" s="374" t="n"/>
+      <c r="I51" s="375" t="n"/>
+      <c r="J51" s="375" t="n"/>
+      <c r="K51" s="375" t="n"/>
+      <c r="L51" s="373" t="n"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="127">
       <c r="A52" s="137" t="inlineStr">
@@ -3629,24 +3668,24 @@
         </is>
       </c>
       <c r="B54" s="97" t="n"/>
-      <c r="C54" s="301" t="n"/>
-      <c r="D54" s="97" t="n"/>
+      <c r="C54" s="374" t="n"/>
+      <c r="D54" s="373" t="n"/>
       <c r="E54" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F54" s="97" t="n"/>
-      <c r="G54" s="301" t="n"/>
-      <c r="H54" s="97" t="n"/>
+      <c r="G54" s="374" t="n"/>
+      <c r="H54" s="373" t="n"/>
       <c r="I54" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J54" s="97" t="n"/>
-      <c r="K54" s="301" t="n"/>
-      <c r="L54" s="97" t="n"/>
+      <c r="K54" s="374" t="n"/>
+      <c r="L54" s="373" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1" s="127">
       <c r="A55" s="302" t="inlineStr">
@@ -3655,24 +3694,24 @@
         </is>
       </c>
       <c r="B55" s="97" t="n"/>
-      <c r="C55" s="301" t="n"/>
-      <c r="D55" s="97" t="n"/>
+      <c r="C55" s="374" t="n"/>
+      <c r="D55" s="373" t="n"/>
       <c r="E55" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F55" s="97" t="n"/>
-      <c r="G55" s="301" t="n"/>
-      <c r="H55" s="97" t="n"/>
+      <c r="G55" s="374" t="n"/>
+      <c r="H55" s="373" t="n"/>
       <c r="I55" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J55" s="97" t="n"/>
-      <c r="K55" s="301" t="n"/>
-      <c r="L55" s="97" t="n"/>
+      <c r="K55" s="374" t="n"/>
+      <c r="L55" s="373" t="n"/>
     </row>
     <row r="56" ht="21" customHeight="1" s="127">
       <c r="A56" s="302" t="inlineStr">
@@ -3681,24 +3720,24 @@
         </is>
       </c>
       <c r="B56" s="97" t="n"/>
-      <c r="C56" s="301" t="n"/>
-      <c r="D56" s="97" t="n"/>
+      <c r="C56" s="374" t="n"/>
+      <c r="D56" s="373" t="n"/>
       <c r="E56" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F56" s="97" t="n"/>
-      <c r="G56" s="301" t="n"/>
-      <c r="H56" s="97" t="n"/>
+      <c r="G56" s="374" t="n"/>
+      <c r="H56" s="373" t="n"/>
       <c r="I56" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J56" s="97" t="n"/>
-      <c r="K56" s="301" t="n"/>
-      <c r="L56" s="97" t="n"/>
+      <c r="K56" s="374" t="n"/>
+      <c r="L56" s="373" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="25" t="inlineStr">
@@ -3712,6 +3751,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="179">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
